--- a/filer/26799945_hay.xlsx
+++ b/filer/26799945_hay.xlsx
@@ -639,7 +639,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision · Regnskabsår 1/6–31/5 (forskudt)</t>
         </is>
       </c>
     </row>

--- a/filer/26799945_hay.xlsx
+++ b/filer/26799945_hay.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4570,6 +4570,13 @@
       <c r="F94" s="13">
         <f>IFERROR($F$36/($F$61+0)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
